--- a/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-26T15:33:36+00:00</t>
+    <t>2025-02-26T15:37:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-26T15:37:29+00:00</t>
+    <t>2025-02-27T22:55:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-27T22:55:39+00:00</t>
+    <t>2025-03-02T19:26:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-02T19:26:20+00:00</t>
+    <t>2025-03-02T19:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-02T19:33:38+00:00</t>
+    <t>2025-03-03T11:01:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-03T11:01:42+00:00</t>
+    <t>2025-03-06T11:29:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T11:29:33+00:00</t>
+    <t>2025-03-06T11:49:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T11:49:07+00:00</t>
+    <t>2025-03-06T20:18:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://www.ehealth.fgov.be/standards/fhir/medication/StructureDefinition/PSSDataAcquisitionForm</t>
+    <t>https://www.ehealth.fgov.be/standards/fhir/pss/StructureDefinition/PSSDataAcquisitionForm</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T20:18:44+00:00</t>
+    <t>2025-03-06T20:59:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1028,7 +1028,7 @@
     <t>CodeValueSet</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://www.ehealth.fgov.be/standards/fhir/medication/StructureDefinition/CodeValueSet}
+    <t xml:space="preserve">Extension {https://www.ehealth.fgov.be/standards/fhir/pss/StructureDefinition/CodeValueSet}
 </t>
   </si>
   <si>
@@ -1811,7 +1811,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="94.8515625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="87.6953125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T20:59:35+00:00</t>
+    <t>2025-03-07T09:02:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-07T09:02:50+00:00</t>
+    <t>2025-03-07T12:27:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-07T12:27:18+00:00</t>
+    <t>2025-03-07T13:27:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-07T13:27:46+00:00</t>
+    <t>2025-03-11T13:06:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T13:06:04+00:00</t>
+    <t>2025-03-11T13:09:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T13:09:22+00:00</t>
+    <t>2025-03-11T13:27:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T13:27:28+00:00</t>
+    <t>2025-03-11T13:28:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T13:28:38+00:00</t>
+    <t>2025-03-11T13:29:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T13:29:42+00:00</t>
+    <t>2025-03-17T15:05:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-17T15:05:50+00:00</t>
+    <t>2025-03-18T10:04:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-18T10:04:30+00:00</t>
+    <t>2025-03-20T11:13:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-20T11:13:27+00:00</t>
+    <t>2025-03-20T15:00:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-20T15:00:12+00:00</t>
+    <t>2025-03-24T10:58:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-24T10:58:19+00:00</t>
+    <t>2025-03-24T11:01:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-24T11:01:08+00:00</t>
+    <t>2025-03-24T11:01:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-24T11:01:18+00:00</t>
+    <t>2025-03-24T12:21:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-24T12:21:29+00:00</t>
+    <t>2025-03-26T10:25:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-26T10:25:04+00:00</t>
+    <t>2025-04-06T05:59:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-06T05:59:28+00:00</t>
+    <t>2025-04-06T06:02:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-06T06:02:42+00:00</t>
+    <t>2025-04-10T08:21:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-10T08:21:04+00:00</t>
+    <t>2025-04-15T15:53:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-15T15:53:54+00:00</t>
+    <t>2025-04-16T11:48:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-16T11:48:10+00:00</t>
+    <t>2025-04-16T11:48:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,22 +57,22 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-16T11:48:51+00:00</t>
+    <t>2025-04-16T12:31:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>HL7 Belgium</t>
+    <t>eHealth Platform Belgium</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>HL7 Belgium (https://www.hl7belgium.org, hl7belgium@hl7belgium.org)</t>
-  </si>
-  <si>
-    <t>Message Structure eHealth (message-structure@ehealth.fgov.be(work))</t>
+    <t>eHealth Platform Belgium (https://www.ehealth.fgov.be/standards/fhir/, support@be-ehealth-standards.atlassian.net)</t>
+  </si>
+  <si>
+    <t>Message Structure eHealth (support@be-ehealth-standards.atlassian.net(work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-16T12:31:30+00:00</t>
+    <t>2025-04-16T12:36:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-16T12:36:28+00:00</t>
+    <t>2025-04-16T12:41:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-16T12:41:18+00:00</t>
+    <t>2025-04-16T13:08:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>active</t>
+    <t>draft</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,22 +57,22 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-16T13:08:49+00:00</t>
+    <t>2025-04-17T08:21:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>eHealth Platform Belgium</t>
+    <t>HL7 Belgium</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>eHealth Platform Belgium (https://www.ehealth.fgov.be/standards/fhir/, support@be-ehealth-standards.atlassian.net)</t>
-  </si>
-  <si>
-    <t>Message Structure eHealth (support@be-ehealth-standards.atlassian.net(work))</t>
+    <t>HL7 Belgium (https://www.hl7belgium.org, hl7belgium@hl7belgium.org)</t>
+  </si>
+  <si>
+    <t>Message Structure eHealth (message-structure@ehealth.fgov.be(work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2538" uniqueCount="471">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2573" uniqueCount="476">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-17T08:21:49+00:00</t>
+    <t>2025-04-17T08:44:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1389,6 +1389,22 @@
   </si>
   <si>
     <t>Questionnaire.item.answerOption.extension</t>
+  </si>
+  <si>
+    <t>Questionnaire.item.answerOption.extension:answerOptionAdditionalCode</t>
+  </si>
+  <si>
+    <t>answerOptionAdditionalCode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://www.ehealth.fgov.be/standards/fhir/pss/StructureDefinition/AnswerOptionAdditionalCode}
+</t>
+  </si>
+  <si>
+    <t>AnswerOption Additional Code</t>
+  </si>
+  <si>
+    <t>An additional code for an option in a choice question</t>
   </si>
   <si>
     <t>Questionnaire.item.answerOption.modifierExtension</t>
@@ -1798,20 +1814,20 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO67"/>
+  <dimension ref="A1:AO68"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="49.16796875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="49.16796875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="13.92578125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="58.9921875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="42.15234375" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="23.7578125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="87.6953125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="87.1171875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1820,27 +1836,27 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="86.3125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="59.6953125" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="45.5390625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="73.99609375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="51.17578125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="39.04296875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="125.9375" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="48.05859375" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="28.1484375" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="107.96875" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="41.19921875" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="24.1328125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8553,7 +8569,7 @@
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>134</v>
+        <v>82</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8575,14 +8591,12 @@
         <v>135</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>136</v>
+        <v>319</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>138</v>
-      </c>
+        <v>320</v>
+      </c>
+      <c r="N58" s="2"/>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>82</v>
@@ -8619,16 +8633,14 @@
         <v>82</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC58" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>321</v>
+      </c>
+      <c r="AC58" s="2"/>
       <c r="AD58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>82</v>
+        <v>322</v>
       </c>
       <c r="AF58" t="s" s="2">
         <v>323</v>
@@ -8649,7 +8661,7 @@
         <v>82</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>317</v>
+        <v>82</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>82</v>
@@ -8666,11 +8678,13 @@
         <v>439</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="C59" s="2"/>
+        <v>438</v>
+      </c>
+      <c r="C59" t="s" s="2">
+        <v>440</v>
+      </c>
       <c r="D59" t="s" s="2">
-        <v>331</v>
+        <v>82</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -8683,26 +8697,22 @@
         <v>82</v>
       </c>
       <c r="I59" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>135</v>
+        <v>441</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>332</v>
+        <v>442</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>144</v>
-      </c>
+        <v>443</v>
+      </c>
+      <c r="N59" s="2"/>
+      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>82</v>
       </c>
@@ -8750,7 +8760,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>334</v>
+        <v>323</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -8759,7 +8769,7 @@
         <v>81</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>82</v>
+        <v>329</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>140</v>
@@ -8768,7 +8778,7 @@
         <v>82</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>132</v>
+        <v>82</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>82</v>
@@ -8782,44 +8792,46 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>82</v>
+        <v>331</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I60" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>441</v>
+        <v>135</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>442</v>
+        <v>332</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>443</v>
+        <v>333</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="O60" s="2"/>
+        <v>138</v>
+      </c>
+      <c r="O60" t="s" s="2">
+        <v>144</v>
+      </c>
       <c r="P60" t="s" s="2">
         <v>82</v>
       </c>
@@ -8843,13 +8855,13 @@
         <v>82</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>301</v>
+        <v>82</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>394</v>
+        <v>82</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>395</v>
+        <v>82</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>82</v>
@@ -8867,25 +8879,25 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>440</v>
+        <v>334</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>370</v>
+        <v>132</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>82</v>
@@ -8910,7 +8922,7 @@
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G61" t="s" s="2">
         <v>89</v>
@@ -8925,24 +8937,22 @@
         <v>82</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>201</v>
+        <v>446</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q61" t="s" s="2">
-        <v>449</v>
-      </c>
+      <c r="Q61" s="2"/>
       <c r="R61" t="s" s="2">
         <v>82</v>
       </c>
@@ -8962,13 +8972,13 @@
         <v>82</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>82</v>
+        <v>301</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>82</v>
+        <v>394</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>82</v>
+        <v>395</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>82</v>
@@ -8989,7 +8999,7 @@
         <v>445</v>
       </c>
       <c r="AG61" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AH61" t="s" s="2">
         <v>89</v>
@@ -9032,7 +9042,7 @@
         <v>80</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>82</v>
@@ -9044,7 +9054,7 @@
         <v>82</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>306</v>
+        <v>201</v>
       </c>
       <c r="L62" t="s" s="2">
         <v>451</v>
@@ -9055,13 +9065,13 @@
       <c r="N62" t="s" s="2">
         <v>453</v>
       </c>
-      <c r="O62" t="s" s="2">
+      <c r="O62" s="2"/>
+      <c r="P62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q62" t="s" s="2">
         <v>454</v>
       </c>
-      <c r="P62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q62" s="2"/>
       <c r="R62" t="s" s="2">
         <v>82</v>
       </c>
@@ -9111,10 +9121,10 @@
         <v>80</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>455</v>
+        <v>82</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>101</v>
@@ -9137,10 +9147,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9151,7 +9161,7 @@
         <v>80</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>82</v>
@@ -9163,16 +9173,20 @@
         <v>82</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>164</v>
+        <v>306</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>314</v>
+        <v>456</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="N63" s="2"/>
-      <c r="O63" s="2"/>
+        <v>457</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="O63" t="s" s="2">
+        <v>459</v>
+      </c>
       <c r="P63" t="s" s="2">
         <v>82</v>
       </c>
@@ -9220,25 +9234,25 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>316</v>
+        <v>455</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>82</v>
+        <v>460</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>82</v>
+        <v>101</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>317</v>
+        <v>370</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>82</v>
@@ -9252,21 +9266,21 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>134</v>
+        <v>82</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>82</v>
@@ -9278,17 +9292,15 @@
         <v>82</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>135</v>
+        <v>164</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>136</v>
+        <v>314</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>138</v>
-      </c>
+        <v>315</v>
+      </c>
+      <c r="N64" s="2"/>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>82</v>
@@ -9337,19 +9349,19 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>140</v>
+        <v>82</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>82</v>
@@ -9369,14 +9381,14 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>331</v>
+        <v>134</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -9389,26 +9401,24 @@
         <v>82</v>
       </c>
       <c r="I65" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="K65" t="s" s="2">
         <v>135</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>332</v>
+        <v>136</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>333</v>
+        <v>379</v>
       </c>
       <c r="N65" t="s" s="2">
         <v>138</v>
       </c>
-      <c r="O65" t="s" s="2">
-        <v>144</v>
-      </c>
+      <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>82</v>
       </c>
@@ -9456,7 +9466,7 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>334</v>
+        <v>323</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -9474,7 +9484,7 @@
         <v>82</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>132</v>
+        <v>317</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>82</v>
@@ -9488,44 +9498,46 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>82</v>
+        <v>331</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I66" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>460</v>
+        <v>135</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>461</v>
+        <v>332</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>462</v>
+        <v>333</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="O66" s="2"/>
+        <v>138</v>
+      </c>
+      <c r="O66" t="s" s="2">
+        <v>144</v>
+      </c>
       <c r="P66" t="s" s="2">
         <v>82</v>
       </c>
@@ -9549,13 +9561,13 @@
         <v>82</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>301</v>
+        <v>82</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>394</v>
+        <v>82</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>395</v>
+        <v>82</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>82</v>
@@ -9573,25 +9585,25 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>459</v>
+        <v>334</v>
       </c>
       <c r="AG66" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>370</v>
+        <v>132</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>82</v>
@@ -9616,10 +9628,10 @@
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>82</v>
@@ -9631,20 +9643,18 @@
         <v>82</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>83</v>
+        <v>465</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="O67" t="s" s="2">
         <v>468</v>
       </c>
+      <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>82</v>
       </c>
@@ -9668,13 +9678,13 @@
         <v>82</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>82</v>
+        <v>301</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>82</v>
+        <v>394</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>82</v>
+        <v>395</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>82</v>
@@ -9695,13 +9705,13 @@
         <v>464</v>
       </c>
       <c r="AG67" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>469</v>
+        <v>82</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>101</v>
@@ -9710,15 +9720,134 @@
         <v>82</v>
       </c>
       <c r="AL67" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="AM67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO67" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="C68" s="2"/>
+      <c r="D68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E68" s="2"/>
+      <c r="F68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="L68" t="s" s="2">
         <v>470</v>
       </c>
-      <c r="AM67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO67" t="s" s="2">
+      <c r="M68" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="O68" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="P68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q68" s="2"/>
+      <c r="R68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF68" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="AG68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI68" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="AM68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO68" t="s" s="2">
         <v>82</v>
       </c>
     </row>

--- a/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-17T08:44:33+00:00</t>
+    <t>2025-04-17T09:22:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-17T09:22:19+00:00</t>
+    <t>2025-04-17T09:39:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-17T09:39:14+00:00</t>
+    <t>2025-04-17T11:28:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,22 +57,22 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-17T11:28:46+00:00</t>
+    <t>2025-04-28T07:30:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>HL7 Belgium</t>
+    <t>eHealth Platform Belgium</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>HL7 Belgium (https://www.hl7belgium.org, hl7belgium@hl7belgium.org)</t>
-  </si>
-  <si>
-    <t>Message Structure eHealth (message-structure@ehealth.fgov.be(work))</t>
+    <t>eHealth Platform Belgium (https://www.ehealth.fgov.be/standards/fhir/, support@be-ehealth-standards.atlassian.net)</t>
+  </si>
+  <si>
+    <t>Message Structure eHealth (support@be-ehealth-standards.atlassian.net(work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T07:30:14+00:00</t>
+    <t>2025-04-28T07:30:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T07:30:51+00:00</t>
+    <t>2025-04-28T07:57:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T07:57:00+00:00</t>
+    <t>2025-04-28T07:57:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T07:57:33+00:00</t>
+    <t>2025-04-28T07:57:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T07:57:44+00:00</t>
+    <t>2025-04-30T14:13:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-30T14:13:57+00:00</t>
+    <t>2025-04-30T14:16:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-30T14:16:07+00:00</t>
+    <t>2025-04-30T14:16:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-30T14:16:39+00:00</t>
+    <t>2025-05-06T09:47:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -9,11 +9,14 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$71</definedName>
+  </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2573" uniqueCount="476">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2684" uniqueCount="491">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-06T09:47:23+00:00</t>
+    <t>2025-05-06T11:05:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -114,7 +117,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Questionnaire</t>
+    <t>http://hl7.org/fhir/uv/cpg/StructureDefinition/cpg-computablequestionnaire</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -1022,6 +1025,42 @@
     <t>Element.extension</t>
   </si>
   <si>
+    <t>Questionnaire.item.extension:answerValueSetSource</t>
+  </si>
+  <si>
+    <t>answerValueSetSource</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://hl7.org/fhir/uv/cpg/StructureDefinition/cpg-answerValueSetSource}
+</t>
+  </si>
+  <si>
+    <t>CPG Answer Value Set Source Extension</t>
+  </si>
+  <si>
+    <t>The canonical URL for the source value set for the answer options, when those options are provided directly in the questionnaire.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>Questionnaire.item.extension:itemImage</t>
+  </si>
+  <si>
+    <t>itemImage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://hl7.org/fhir/uv/cpg/StructureDefinition/cpg-itemImage}
+</t>
+  </si>
+  <si>
+    <t>CPG Item Image Extension</t>
+  </si>
+  <si>
+    <t>An image to display as a visual accompaniment to the question being asked.</t>
+  </si>
+  <si>
     <t>Questionnaire.item.extension:CodeValueSet</t>
   </si>
   <si>
@@ -1036,10 +1075,6 @@
   </si>
   <si>
     <t>A ValueSet used when a question / item can correspond not just to a single code but to a set of concepts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1
-</t>
   </si>
   <si>
     <t>Questionnaire.item.modifierExtension</t>
@@ -1389,6 +1424,22 @@
   </si>
   <si>
     <t>Questionnaire.item.answerOption.extension</t>
+  </si>
+  <si>
+    <t>Questionnaire.item.answerOption.extension:responseImage</t>
+  </si>
+  <si>
+    <t>responseImage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://hl7.org/fhir/uv/cpg/StructureDefinition/cpg-responseImage}
+</t>
+  </si>
+  <si>
+    <t>CPG Response Image Extension</t>
+  </si>
+  <si>
+    <t>An image to display as a visual accompaniment to the response.</t>
   </si>
   <si>
     <t>Questionnaire.item.answerOption.extension:answerOptionAdditionalCode</t>
@@ -1633,6 +1684,21 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="22"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color indexed="22"/>
+        <i val="true"/>
+      </font>
+    </dxf>
+  </dxfs>
 </styleSheet>
 </file>
 
@@ -1814,7 +1880,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO68"/>
+  <dimension ref="A1:AO71"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="58.9921875" customWidth="true" bestFit="true"/>
@@ -1984,7 +2050,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
         <v>31</v>
       </c>
@@ -2099,7 +2165,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
         <v>88</v>
       </c>
@@ -2216,7 +2282,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
         <v>96</v>
       </c>
@@ -2331,7 +2397,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
         <v>102</v>
       </c>
@@ -2448,7 +2514,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
         <v>108</v>
       </c>
@@ -2565,7 +2631,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
         <v>117</v>
       </c>
@@ -2682,7 +2748,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
         <v>125</v>
       </c>
@@ -2799,7 +2865,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
         <v>133</v>
       </c>
@@ -2916,7 +2982,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
         <v>141</v>
       </c>
@@ -3035,7 +3101,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
         <v>146</v>
       </c>
@@ -3154,7 +3220,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
         <v>154</v>
       </c>
@@ -3273,7 +3339,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
         <v>163</v>
       </c>
@@ -3390,7 +3456,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
         <v>171</v>
       </c>
@@ -3509,7 +3575,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
         <v>177</v>
       </c>
@@ -3626,7 +3692,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
         <v>183</v>
       </c>
@@ -3743,7 +3809,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
         <v>190</v>
       </c>
@@ -3860,7 +3926,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
         <v>200</v>
       </c>
@@ -3979,7 +4045,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
         <v>207</v>
       </c>
@@ -4096,7 +4162,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
         <v>215</v>
       </c>
@@ -4213,7 +4279,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
         <v>224</v>
       </c>
@@ -4332,7 +4398,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
         <v>232</v>
       </c>
@@ -4449,7 +4515,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
         <v>239</v>
       </c>
@@ -4566,7 +4632,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
         <v>246</v>
       </c>
@@ -4685,7 +4751,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
         <v>253</v>
       </c>
@@ -4802,7 +4868,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
         <v>262</v>
       </c>
@@ -4919,7 +4985,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
         <v>269</v>
       </c>
@@ -5036,7 +5102,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
         <v>275</v>
       </c>
@@ -5153,7 +5219,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
         <v>282</v>
       </c>
@@ -5272,7 +5338,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
         <v>289</v>
       </c>
@@ -5391,7 +5457,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
         <v>296</v>
       </c>
@@ -5508,7 +5574,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
         <v>305</v>
       </c>
@@ -5527,7 +5593,7 @@
         <v>81</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>82</v>
@@ -5625,7 +5691,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
         <v>313</v>
       </c>
@@ -5740,7 +5806,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
         <v>318</v>
       </c>
@@ -5853,7 +5919,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
         <v>324</v>
       </c>
@@ -5874,7 +5940,7 @@
         <v>89</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>82</v>
@@ -5970,48 +6036,46 @@
         <v>82</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
         <v>330</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="C36" s="2"/>
+        <v>318</v>
+      </c>
+      <c r="C36" t="s" s="2">
+        <v>331</v>
+      </c>
       <c r="D36" t="s" s="2">
-        <v>331</v>
+        <v>82</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="I36" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>135</v>
+        <v>332</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>144</v>
-      </c>
+        <v>334</v>
+      </c>
+      <c r="N36" s="2"/>
+      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>82</v>
       </c>
@@ -6059,7 +6123,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>334</v>
+        <v>323</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6068,7 +6132,7 @@
         <v>81</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>82</v>
+        <v>329</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>140</v>
@@ -6077,7 +6141,7 @@
         <v>82</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>132</v>
+        <v>82</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>82</v>
@@ -6089,20 +6153,22 @@
         <v>82</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
         <v>335</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="C37" s="2"/>
+        <v>318</v>
+      </c>
+      <c r="C37" t="s" s="2">
+        <v>336</v>
+      </c>
       <c r="D37" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G37" t="s" s="2">
         <v>89</v>
@@ -6117,20 +6183,16 @@
         <v>82</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>164</v>
+        <v>337</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="O37" t="s" s="2">
         <v>339</v>
       </c>
+      <c r="N37" s="2"/>
+      <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>82</v>
       </c>
@@ -6178,65 +6240,65 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>335</v>
+        <v>323</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL37" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM37" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN37" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO37" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="38" hidden="true">
+      <c r="A38" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="AM37" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN37" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO37" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="s" s="2">
-        <v>341</v>
-      </c>
       <c r="B38" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>82</v>
+        <v>341</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I38" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>103</v>
+        <v>135</v>
       </c>
       <c r="L38" t="s" s="2">
         <v>342</v>
@@ -6245,10 +6307,10 @@
         <v>343</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>344</v>
+        <v>138</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>345</v>
+        <v>144</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>82</v>
@@ -6297,25 +6359,25 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>346</v>
+        <v>132</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>82</v>
@@ -6327,12 +6389,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6340,10 +6402,10 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>82</v>
@@ -6355,19 +6417,19 @@
         <v>82</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>297</v>
+        <v>164</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="M39" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="N39" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="O39" t="s" s="2">
         <v>349</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>351</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>82</v>
@@ -6392,13 +6454,13 @@
         <v>82</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>301</v>
+        <v>82</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>302</v>
+        <v>82</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>303</v>
+        <v>82</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>82</v>
@@ -6416,16 +6478,16 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>310</v>
+        <v>82</v>
       </c>
       <c r="AJ39" t="s" s="2">
         <v>101</v>
@@ -6434,7 +6496,7 @@
         <v>82</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>304</v>
+        <v>350</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>82</v>
@@ -6446,16 +6508,16 @@
         <v>82</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>353</v>
+        <v>82</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6474,19 +6536,19 @@
         <v>82</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>164</v>
+        <v>103</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="M40" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="N40" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="M40" t="s" s="2">
+      <c r="O40" t="s" s="2">
         <v>355</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>82</v>
@@ -6535,7 +6597,7 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6553,7 +6615,7 @@
         <v>82</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>82</v>
@@ -6565,12 +6627,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6581,7 +6643,7 @@
         <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>82</v>
@@ -6593,18 +6655,20 @@
         <v>82</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>164</v>
+        <v>297</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="M41" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="N41" t="s" s="2">
         <v>360</v>
       </c>
-      <c r="M41" t="s" s="2">
+      <c r="O41" t="s" s="2">
         <v>361</v>
       </c>
-      <c r="N41" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>82</v>
       </c>
@@ -6628,13 +6692,13 @@
         <v>82</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>82</v>
+        <v>301</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>82</v>
+        <v>302</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>82</v>
+        <v>303</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>82</v>
@@ -6652,16 +6716,16 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>82</v>
+        <v>310</v>
       </c>
       <c r="AJ41" t="s" s="2">
         <v>101</v>
@@ -6670,7 +6734,7 @@
         <v>82</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>245</v>
+        <v>304</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>82</v>
@@ -6682,20 +6746,20 @@
         <v>82</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>82</v>
+        <v>363</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G42" t="s" s="2">
         <v>89</v>
@@ -6710,7 +6774,7 @@
         <v>82</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>109</v>
+        <v>164</v>
       </c>
       <c r="L42" t="s" s="2">
         <v>364</v>
@@ -6747,13 +6811,13 @@
         <v>82</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>194</v>
+        <v>82</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>368</v>
+        <v>82</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>369</v>
+        <v>82</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>82</v>
@@ -6771,10 +6835,10 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AH42" t="s" s="2">
         <v>89</v>
@@ -6789,7 +6853,7 @@
         <v>82</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>82</v>
@@ -6801,12 +6865,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6817,32 +6881,30 @@
         <v>80</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="J43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>306</v>
+        <v>164</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="M43" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="N43" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="M43" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>375</v>
-      </c>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>82</v>
       </c>
@@ -6890,25 +6952,25 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>376</v>
+        <v>101</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>370</v>
+        <v>245</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>82</v>
@@ -6920,12 +6982,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6933,7 +6995,7 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G44" t="s" s="2">
         <v>89</v>
@@ -6948,16 +7010,20 @@
         <v>82</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>164</v>
+        <v>109</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>314</v>
+        <v>374</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="N44" s="2"/>
-      <c r="O44" s="2"/>
+        <v>375</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="O44" t="s" s="2">
+        <v>377</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>82</v>
       </c>
@@ -6981,13 +7047,13 @@
         <v>82</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>82</v>
+        <v>194</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>82</v>
+        <v>378</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>82</v>
+        <v>379</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>82</v>
@@ -7005,10 +7071,10 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>316</v>
+        <v>373</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AH44" t="s" s="2">
         <v>89</v>
@@ -7017,13 +7083,13 @@
         <v>82</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>82</v>
+        <v>101</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>317</v>
+        <v>380</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>82</v>
@@ -7035,16 +7101,16 @@
         <v>82</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>134</v>
+        <v>82</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -7057,24 +7123,26 @@
         <v>82</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="J45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>135</v>
+        <v>306</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>136</v>
+        <v>382</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O45" s="2"/>
+        <v>384</v>
+      </c>
+      <c r="O45" t="s" s="2">
+        <v>385</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>82</v>
       </c>
@@ -7122,7 +7190,7 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>323</v>
+        <v>381</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7134,13 +7202,13 @@
         <v>82</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>140</v>
+        <v>386</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>317</v>
+        <v>380</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>82</v>
@@ -7152,48 +7220,44 @@
         <v>82</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>380</v>
+        <v>387</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>380</v>
+        <v>387</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>331</v>
+        <v>82</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I46" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>135</v>
+        <v>164</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>332</v>
+        <v>314</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>144</v>
-      </c>
+        <v>315</v>
+      </c>
+      <c r="N46" s="2"/>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>82</v>
       </c>
@@ -7241,25 +7305,25 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>334</v>
+        <v>316</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>140</v>
+        <v>82</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>132</v>
+        <v>317</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>82</v>
@@ -7271,23 +7335,23 @@
         <v>82</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>82</v>
+        <v>134</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>82</v>
@@ -7299,16 +7363,16 @@
         <v>82</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>164</v>
+        <v>135</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>382</v>
+        <v>136</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>384</v>
+        <v>138</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7358,25 +7422,25 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>381</v>
+        <v>323</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>370</v>
+        <v>317</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>82</v>
@@ -7388,44 +7452,48 @@
         <v>82</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>82</v>
+        <v>341</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I48" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>109</v>
+        <v>135</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>386</v>
+        <v>342</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="N48" s="2"/>
-      <c r="O48" s="2"/>
+        <v>343</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="O48" t="s" s="2">
+        <v>144</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>82</v>
       </c>
@@ -7449,13 +7517,13 @@
         <v>82</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>194</v>
+        <v>82</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>388</v>
+        <v>82</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>389</v>
+        <v>82</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>82</v>
@@ -7473,25 +7541,25 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>385</v>
+        <v>344</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>370</v>
+        <v>132</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>82</v>
@@ -7503,12 +7571,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7531,7 +7599,7 @@
         <v>82</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>391</v>
+        <v>164</v>
       </c>
       <c r="L49" t="s" s="2">
         <v>392</v>
@@ -7539,7 +7607,9 @@
       <c r="M49" t="s" s="2">
         <v>393</v>
       </c>
-      <c r="N49" s="2"/>
+      <c r="N49" t="s" s="2">
+        <v>394</v>
+      </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>82</v>
@@ -7564,13 +7634,13 @@
         <v>82</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>301</v>
+        <v>82</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>394</v>
+        <v>82</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>395</v>
+        <v>82</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>82</v>
@@ -7588,7 +7658,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>89</v>
@@ -7597,7 +7667,7 @@
         <v>89</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>396</v>
+        <v>82</v>
       </c>
       <c r="AJ49" t="s" s="2">
         <v>101</v>
@@ -7606,7 +7676,7 @@
         <v>82</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>82</v>
@@ -7618,12 +7688,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7631,7 +7701,7 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G50" t="s" s="2">
         <v>89</v>
@@ -7649,14 +7719,12 @@
         <v>109</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>400</v>
-      </c>
+        <v>397</v>
+      </c>
+      <c r="N50" s="2"/>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>82</v>
@@ -7684,11 +7752,11 @@
         <v>194</v>
       </c>
       <c r="Y50" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="Z50" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="Z50" t="s" s="2">
-        <v>401</v>
-      </c>
       <c r="AA50" t="s" s="2">
         <v>82</v>
       </c>
@@ -7705,16 +7773,16 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AH50" t="s" s="2">
         <v>89</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>402</v>
+        <v>82</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>101</v>
@@ -7723,7 +7791,7 @@
         <v>82</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>82</v>
@@ -7735,12 +7803,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7748,7 +7816,7 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G51" t="s" s="2">
         <v>89</v>
@@ -7763,24 +7831,20 @@
         <v>82</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>201</v>
+        <v>401</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>406</v>
-      </c>
+        <v>403</v>
+      </c>
+      <c r="N51" s="2"/>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q51" t="s" s="2">
-        <v>407</v>
-      </c>
+      <c r="Q51" s="2"/>
       <c r="R51" t="s" s="2">
         <v>82</v>
       </c>
@@ -7800,13 +7864,13 @@
         <v>82</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>82</v>
+        <v>301</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>82</v>
+        <v>404</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>82</v>
+        <v>405</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>82</v>
@@ -7824,16 +7888,16 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AH51" t="s" s="2">
         <v>89</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="AJ51" t="s" s="2">
         <v>101</v>
@@ -7842,7 +7906,7 @@
         <v>82</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>82</v>
@@ -7854,12 +7918,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7882,53 +7946,49 @@
         <v>82</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>201</v>
+        <v>109</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="M52" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="N52" t="s" s="2">
         <v>410</v>
       </c>
-      <c r="M52" t="s" s="2">
+      <c r="O52" s="2"/>
+      <c r="P52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q52" s="2"/>
+      <c r="R52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X52" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="Z52" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="N52" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="P52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q52" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="R52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z52" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AA52" t="s" s="2">
         <v>82</v>
       </c>
@@ -7945,7 +8005,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -7954,7 +8014,7 @@
         <v>89</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>101</v>
@@ -7963,7 +8023,7 @@
         <v>82</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>82</v>
@@ -7975,12 +8035,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8006,21 +8066,21 @@
         <v>201</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="M53" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="N53" t="s" s="2">
         <v>416</v>
       </c>
-      <c r="M53" t="s" s="2">
+      <c r="O53" s="2"/>
+      <c r="P53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q53" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="N53" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="P53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q53" s="2"/>
       <c r="R53" t="s" s="2">
         <v>82</v>
       </c>
@@ -8064,7 +8124,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8073,7 +8133,7 @@
         <v>89</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>101</v>
@@ -8082,7 +8142,7 @@
         <v>82</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>82</v>
@@ -8094,12 +8154,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8122,22 +8182,26 @@
         <v>82</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="L54" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="N54" t="s" s="2">
         <v>422</v>
       </c>
-      <c r="L54" t="s" s="2">
+      <c r="O54" t="s" s="2">
         <v>423</v>
       </c>
-      <c r="M54" t="s" s="2">
+      <c r="P54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q54" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="N54" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="O54" s="2"/>
-      <c r="P54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q54" s="2"/>
       <c r="R54" t="s" s="2">
         <v>82</v>
       </c>
@@ -8181,7 +8245,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8190,7 +8254,7 @@
         <v>89</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="AJ54" t="s" s="2">
         <v>101</v>
@@ -8199,7 +8263,7 @@
         <v>82</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>82</v>
@@ -8208,15 +8272,15 @@
         <v>82</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>132</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8239,18 +8303,20 @@
         <v>82</v>
       </c>
       <c r="K55" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="L55" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="N55" t="s" s="2">
         <v>428</v>
       </c>
-      <c r="L55" t="s" s="2">
+      <c r="O55" t="s" s="2">
         <v>429</v>
       </c>
-      <c r="M55" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>82</v>
       </c>
@@ -8298,7 +8364,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8307,7 +8373,7 @@
         <v>89</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>101</v>
@@ -8316,7 +8382,7 @@
         <v>82</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>82</v>
@@ -8328,12 +8394,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8344,7 +8410,7 @@
         <v>80</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>82</v>
@@ -8356,16 +8422,16 @@
         <v>82</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>306</v>
+        <v>432</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>434</v>
       </c>
-      <c r="M56" t="s" s="2">
+      <c r="N56" t="s" s="2">
         <v>435</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>436</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8415,16 +8481,16 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>101</v>
@@ -8433,7 +8499,7 @@
         <v>82</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>82</v>
@@ -8442,10 +8508,10 @@
         <v>82</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>82</v>
+        <v>132</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
         <v>437</v>
       </c>
@@ -8473,15 +8539,17 @@
         <v>82</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>164</v>
+        <v>438</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>314</v>
+        <v>439</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="N57" s="2"/>
+        <v>440</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>441</v>
+      </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>82</v>
@@ -8530,7 +8598,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>316</v>
+        <v>437</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -8539,16 +8607,16 @@
         <v>89</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>82</v>
+        <v>442</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>82</v>
+        <v>101</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>317</v>
+        <v>380</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>82</v>
@@ -8560,12 +8628,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8579,7 +8647,7 @@
         <v>81</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>82</v>
@@ -8588,15 +8656,17 @@
         <v>82</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>135</v>
+        <v>306</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>319</v>
+        <v>444</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="N58" s="2"/>
+        <v>445</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>446</v>
+      </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>82</v>
@@ -8633,17 +8703,19 @@
         <v>82</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="AC58" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>322</v>
+        <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>323</v>
+        <v>443</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -8652,16 +8724,16 @@
         <v>81</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>82</v>
+        <v>442</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>82</v>
+        <v>380</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>82</v>
@@ -8673,16 +8745,14 @@
         <v>82</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>439</v>
+        <v>447</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="C59" t="s" s="2">
-        <v>440</v>
-      </c>
+        <v>447</v>
+      </c>
+      <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
         <v>82</v>
       </c>
@@ -8691,7 +8761,7 @@
         <v>80</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>82</v>
@@ -8703,13 +8773,13 @@
         <v>82</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>441</v>
+        <v>164</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>442</v>
+        <v>314</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>443</v>
+        <v>315</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8760,25 +8830,25 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>329</v>
+        <v>82</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>140</v>
+        <v>82</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>82</v>
+        <v>317</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>82</v>
@@ -8790,16 +8860,16 @@
         <v>82</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>331</v>
+        <v>82</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -8812,26 +8882,22 @@
         <v>82</v>
       </c>
       <c r="I60" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="K60" t="s" s="2">
         <v>135</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>332</v>
+        <v>319</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>144</v>
-      </c>
+        <v>320</v>
+      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>82</v>
       </c>
@@ -8867,19 +8933,17 @@
         <v>82</v>
       </c>
       <c r="AB60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC60" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>321</v>
+      </c>
+      <c r="AC60" s="2"/>
       <c r="AD60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE60" t="s" s="2">
-        <v>82</v>
+        <v>322</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>334</v>
+        <v>323</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -8897,7 +8961,7 @@
         <v>82</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>132</v>
+        <v>82</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>82</v>
@@ -8909,26 +8973,28 @@
         <v>82</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="C61" s="2"/>
+        <v>448</v>
+      </c>
+      <c r="C61" t="s" s="2">
+        <v>450</v>
+      </c>
       <c r="D61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G61" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H61" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="I61" t="s" s="2">
         <v>82</v>
@@ -8937,17 +9003,15 @@
         <v>82</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>449</v>
-      </c>
+        <v>453</v>
+      </c>
+      <c r="N61" s="2"/>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>82</v>
@@ -8972,13 +9036,13 @@
         <v>82</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>301</v>
+        <v>82</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>394</v>
+        <v>82</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>395</v>
+        <v>82</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>82</v>
@@ -8996,25 +9060,25 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>445</v>
+        <v>323</v>
       </c>
       <c r="AG61" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>82</v>
+        <v>329</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>370</v>
+        <v>82</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>82</v>
@@ -9026,14 +9090,16 @@
         <v>82</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="C62" s="2"/>
+        <v>448</v>
+      </c>
+      <c r="C62" t="s" s="2">
+        <v>455</v>
+      </c>
       <c r="D62" t="s" s="2">
         <v>82</v>
       </c>
@@ -9042,7 +9108,7 @@
         <v>80</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>82</v>
@@ -9054,24 +9120,20 @@
         <v>82</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>201</v>
+        <v>456</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>453</v>
-      </c>
+        <v>458</v>
+      </c>
+      <c r="N62" s="2"/>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q62" t="s" s="2">
-        <v>454</v>
-      </c>
+      <c r="Q62" s="2"/>
       <c r="R62" t="s" s="2">
         <v>82</v>
       </c>
@@ -9115,25 +9177,25 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>450</v>
+        <v>323</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>370</v>
+        <v>82</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>82</v>
@@ -9145,16 +9207,16 @@
         <v>82</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>82</v>
+        <v>341</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -9167,25 +9229,25 @@
         <v>82</v>
       </c>
       <c r="I63" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>306</v>
+        <v>135</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>456</v>
+        <v>342</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>457</v>
+        <v>343</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>458</v>
+        <v>138</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>459</v>
+        <v>144</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>82</v>
@@ -9234,7 +9296,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>455</v>
+        <v>344</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9243,33 +9305,33 @@
         <v>81</v>
       </c>
       <c r="AI63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AM63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO63" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="64" hidden="true">
+      <c r="A64" t="s" s="2">
         <v>460</v>
       </c>
-      <c r="AJ63" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL63" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="AM63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO63" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="s" s="2">
-        <v>461</v>
-      </c>
       <c r="B64" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9277,7 +9339,7 @@
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G64" t="s" s="2">
         <v>89</v>
@@ -9292,15 +9354,17 @@
         <v>82</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>164</v>
+        <v>461</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>314</v>
+        <v>462</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="N64" s="2"/>
+        <v>463</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>464</v>
+      </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>82</v>
@@ -9325,13 +9389,13 @@
         <v>82</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>82</v>
+        <v>301</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>82</v>
+        <v>404</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>82</v>
+        <v>405</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>82</v>
@@ -9349,10 +9413,10 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>316</v>
+        <v>460</v>
       </c>
       <c r="AG64" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AH64" t="s" s="2">
         <v>89</v>
@@ -9361,13 +9425,13 @@
         <v>82</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>82</v>
+        <v>101</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>317</v>
+        <v>380</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>82</v>
@@ -9379,23 +9443,23 @@
         <v>82</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>134</v>
+        <v>82</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>82</v>
@@ -9407,22 +9471,24 @@
         <v>82</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>135</v>
+        <v>201</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>136</v>
+        <v>466</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>379</v>
+        <v>467</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>138</v>
+        <v>468</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q65" s="2"/>
+      <c r="Q65" t="s" s="2">
+        <v>469</v>
+      </c>
       <c r="R65" t="s" s="2">
         <v>82</v>
       </c>
@@ -9466,25 +9532,25 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>323</v>
+        <v>465</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>317</v>
+        <v>380</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>82</v>
@@ -9496,16 +9562,16 @@
         <v>82</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>463</v>
+        <v>470</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>463</v>
+        <v>470</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>331</v>
+        <v>82</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -9518,25 +9584,25 @@
         <v>82</v>
       </c>
       <c r="I66" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>135</v>
+        <v>306</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>332</v>
+        <v>471</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>333</v>
+        <v>472</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>138</v>
+        <v>473</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>144</v>
+        <v>474</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>82</v>
@@ -9585,7 +9651,7 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>334</v>
+        <v>470</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -9594,16 +9660,16 @@
         <v>81</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>82</v>
+        <v>475</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>132</v>
+        <v>380</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>82</v>
@@ -9615,12 +9681,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>464</v>
+        <v>476</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>464</v>
+        <v>476</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9628,7 +9694,7 @@
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G67" t="s" s="2">
         <v>89</v>
@@ -9643,17 +9709,15 @@
         <v>82</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>465</v>
+        <v>164</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>466</v>
+        <v>314</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>468</v>
-      </c>
+        <v>315</v>
+      </c>
+      <c r="N67" s="2"/>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>82</v>
@@ -9678,13 +9742,13 @@
         <v>82</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>301</v>
+        <v>82</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>394</v>
+        <v>82</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>395</v>
+        <v>82</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>82</v>
@@ -9702,10 +9766,10 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>464</v>
+        <v>316</v>
       </c>
       <c r="AG67" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AH67" t="s" s="2">
         <v>89</v>
@@ -9714,13 +9778,13 @@
         <v>82</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>101</v>
+        <v>82</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>370</v>
+        <v>317</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>82</v>
@@ -9732,16 +9796,16 @@
         <v>82</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>82</v>
+        <v>134</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -9760,20 +9824,18 @@
         <v>82</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>83</v>
+        <v>135</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>470</v>
+        <v>136</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>471</v>
+        <v>389</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>473</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>82</v>
       </c>
@@ -9821,7 +9883,7 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>469</v>
+        <v>323</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -9830,28 +9892,401 @@
         <v>81</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>474</v>
+        <v>82</v>
       </c>
       <c r="AJ68" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="AM68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO68" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="69" hidden="true">
+      <c r="A69" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="C69" s="2"/>
+      <c r="D69" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="E69" s="2"/>
+      <c r="F69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I69" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="J69" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K69" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="O69" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="P69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q69" s="2"/>
+      <c r="R69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF69" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AM69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO69" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="70" hidden="true">
+      <c r="A70" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="C70" s="2"/>
+      <c r="D70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E70" s="2"/>
+      <c r="F70" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G70" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K70" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="O70" s="2"/>
+      <c r="P70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q70" s="2"/>
+      <c r="R70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X70" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="Z70" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF70" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="AG70" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AH70" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
         <v>101</v>
       </c>
-      <c r="AK68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL68" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="AM68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO68" t="s" s="2">
+      <c r="AK70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="AM70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO70" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="71" hidden="true">
+      <c r="A71" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="C71" s="2"/>
+      <c r="D71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E71" s="2"/>
+      <c r="F71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="O71" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="P71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q71" s="2"/>
+      <c r="R71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF71" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="AG71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI71" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="AJ71" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO71" t="s" s="2">
         <v>82</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AO71">
+    <filterColumn colId="6">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+    <filterColumn colId="26">
+      <filters blank="true"/>
+    </filterColumn>
+  </autoFilter>
+  <conditionalFormatting sqref="A2:AI70">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>$G2&lt;&gt;"Y"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$Q2&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-06T11:05:16+00:00</t>
+    <t>2025-05-06T11:11:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-06T11:11:40+00:00</t>
+    <t>2025-05-12T10:14:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -75,7 +75,7 @@
     <t>eHealth Platform Belgium (https://www.ehealth.fgov.be/standards/fhir/, support@be-ehealth-standards.atlassian.net)</t>
   </si>
   <si>
-    <t>Message Structure eHealth (support@be-ehealth-standards.atlassian.net(work))</t>
+    <t>Message Structure eHealth (support@be-ehealth-standards.atlassian.net(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-12T10:14:30+00:00</t>
+    <t>2025-05-12T19:48:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-12T19:50:51+00:00</t>
+    <t>2025-05-12T19:54:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-12T19:54:00+00:00</t>
+    <t>2025-05-13T10:14:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-13T10:14:10+00:00</t>
+    <t>2025-05-13T10:14:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-13T10:14:30+00:00</t>
+    <t>2025-05-13T11:53:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-13T11:53:59+00:00</t>
+    <t>2025-05-13T11:54:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-13T11:54:01+00:00</t>
+    <t>2025-05-13T11:55:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -66,22 +66,22 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-13T11:55:17+00:00</t>
+    <t>2025-05-14T06:43:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>eHealth Platform Belgium</t>
+    <t>eHealth Platform</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>eHealth Platform Belgium (https://www.ehealth.fgov.be/standards/fhir/, support@be-ehealth-standards.atlassian.net)</t>
-  </si>
-  <si>
-    <t>Message Structure eHealth (support@be-ehealth-standards.atlassian.net(Work))</t>
+    <t>eHealth Platform (http://www.ehealth.fgov.be/, support@be-ehealth-standards.atlassian.net)</t>
+  </si>
+  <si>
+    <t>Message Structure (support@be-ehealth-standards.atlassian.net(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -66,22 +66,22 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T06:43:44+00:00</t>
+    <t>2025-05-14T06:55:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>eHealth Platform</t>
+    <t>eHealth Platform Belgium</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>eHealth Platform (http://www.ehealth.fgov.be/, support@be-ehealth-standards.atlassian.net)</t>
-  </si>
-  <si>
-    <t>Message Structure (support@be-ehealth-standards.atlassian.net(Work))</t>
+    <t>eHealth Platform Belgium (https://www.ehealth.fgov.be/standards/fhir/, support@be-ehealth-standards.atlassian.net)</t>
+  </si>
+  <si>
+    <t>Message Structure eHealth (support@be-ehealth-standards.atlassian.net(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T06:55:09+00:00</t>
+    <t>2025-05-14T06:55:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -66,22 +66,22 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T06:55:38+00:00</t>
+    <t>2025-05-14T06:56:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>eHealth Platform Belgium</t>
+    <t>eHealth Platform</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>eHealth Platform Belgium (https://www.ehealth.fgov.be/standards/fhir/, support@be-ehealth-standards.atlassian.net)</t>
-  </si>
-  <si>
-    <t>Message Structure eHealth (support@be-ehealth-standards.atlassian.net(Work))</t>
+    <t>eHealth Platform (http://www.ehealth.fgov.be/, support@be-ehealth-standards.atlassian.net)</t>
+  </si>
+  <si>
+    <t>Message Structure (support@be-ehealth-standards.atlassian.net(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -66,22 +66,22 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T06:56:25+00:00</t>
+    <t>2025-05-14T07:28:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>eHealth Platform</t>
+    <t>eHealth Platform Belgium</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>eHealth Platform (http://www.ehealth.fgov.be/, support@be-ehealth-standards.atlassian.net)</t>
-  </si>
-  <si>
-    <t>Message Structure (support@be-ehealth-standards.atlassian.net(Work))</t>
+    <t>eHealth Platform Belgium (https://www.ehealth.fgov.be/standards/fhir/, support@be-ehealth-standards.atlassian.net)</t>
+  </si>
+  <si>
+    <t>Message Structure eHealth (support@be-ehealth-standards.atlassian.net(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -66,22 +66,22 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T07:28:26+00:00</t>
+    <t>2025-05-14T07:30:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>eHealth Platform Belgium</t>
+    <t>eHealth Platform</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>eHealth Platform Belgium (https://www.ehealth.fgov.be/standards/fhir/, support@be-ehealth-standards.atlassian.net)</t>
-  </si>
-  <si>
-    <t>Message Structure eHealth (support@be-ehealth-standards.atlassian.net(Work))</t>
+    <t>eHealth Platform (http://www.ehealth.fgov.be/, support@be-ehealth-standards.atlassian.net)</t>
+  </si>
+  <si>
+    <t>Message Structure (support@be-ehealth-standards.atlassian.net(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -66,22 +66,22 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T07:30:16+00:00</t>
+    <t>2025-05-14T07:30:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>eHealth Platform</t>
+    <t>eHealth Platform Belgium</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>eHealth Platform (http://www.ehealth.fgov.be/, support@be-ehealth-standards.atlassian.net)</t>
-  </si>
-  <si>
-    <t>Message Structure (support@be-ehealth-standards.atlassian.net(Work))</t>
+    <t>eHealth Platform Belgium (https://www.ehealth.fgov.be/standards/fhir/, support@be-ehealth-standards.atlassian.net)</t>
+  </si>
+  <si>
+    <t>Message Structure eHealth (support@be-ehealth-standards.atlassian.net(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -66,22 +66,22 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T07:30:17+00:00</t>
+    <t>2025-05-14T07:38:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>eHealth Platform Belgium</t>
+    <t>eHealth Platform</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>eHealth Platform Belgium (https://www.ehealth.fgov.be/standards/fhir/, support@be-ehealth-standards.atlassian.net)</t>
-  </si>
-  <si>
-    <t>Message Structure eHealth (support@be-ehealth-standards.atlassian.net(Work))</t>
+    <t>eHealth Platform (http://www.ehealth.fgov.be/, support@be-ehealth-standards.atlassian.net)</t>
+  </si>
+  <si>
+    <t>Message Structure (support@be-ehealth-standards.atlassian.net(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -66,22 +66,22 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T07:38:16+00:00</t>
+    <t>2025-05-14T07:51:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>eHealth Platform</t>
+    <t>eHealth Platform Belgium</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>eHealth Platform (http://www.ehealth.fgov.be/, support@be-ehealth-standards.atlassian.net)</t>
-  </si>
-  <si>
-    <t>Message Structure (support@be-ehealth-standards.atlassian.net(Work))</t>
+    <t>eHealth Platform Belgium (https://www.ehealth.fgov.be/standards/fhir/, support@be-ehealth-standards.atlassian.net)</t>
+  </si>
+  <si>
+    <t>Message Structure eHealth (support@be-ehealth-standards.atlassian.net(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T07:51:32+00:00</t>
+    <t>2025-05-14T07:52:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -66,22 +66,22 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T07:52:33+00:00</t>
+    <t>2025-05-14T07:53:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>eHealth Platform Belgium</t>
+    <t>eHealth Platform</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>eHealth Platform Belgium (https://www.ehealth.fgov.be/standards/fhir/, support@be-ehealth-standards.atlassian.net)</t>
-  </si>
-  <si>
-    <t>Message Structure eHealth (support@be-ehealth-standards.atlassian.net(Work))</t>
+    <t>eHealth Platform (http://www.ehealth.fgov.be/, support@be-ehealth-standards.atlassian.net)</t>
+  </si>
+  <si>
+    <t>Message Structure (support@be-ehealth-standards.atlassian.net(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T07:53:22+00:00</t>
+    <t>2025-05-14T08:06:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T08:06:44+00:00</t>
+    <t>2025-05-14T08:53:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -66,22 +66,22 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T08:53:34+00:00</t>
+    <t>2025-05-14T08:54:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>eHealth Platform</t>
+    <t>eHealth Platform Belgium</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>eHealth Platform (http://www.ehealth.fgov.be/, support@be-ehealth-standards.atlassian.net)</t>
-  </si>
-  <si>
-    <t>Message Structure (support@be-ehealth-standards.atlassian.net(Work))</t>
+    <t>eHealth Platform Belgium (https://www.ehealth.fgov.be/standards/fhir/, support@be-ehealth-standards.atlassian.net)</t>
+  </si>
+  <si>
+    <t>Message Structure eHealth (support@be-ehealth-standards.atlassian.net(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T08:54:50+00:00</t>
+    <t>2025-05-14T09:05:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T09:05:29+00:00</t>
+    <t>2025-05-14T13:37:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T13:37:41+00:00</t>
+    <t>2025-05-14T14:59:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -66,22 +66,22 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T14:59:57+00:00</t>
+    <t>2025-05-14T15:00:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>eHealth Platform Belgium</t>
+    <t>eHealth Platform</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>eHealth Platform Belgium (https://www.ehealth.fgov.be/standards/fhir/, support@be-ehealth-standards.atlassian.net)</t>
-  </si>
-  <si>
-    <t>Message Structure eHealth (support@be-ehealth-standards.atlassian.net(Work))</t>
+    <t>eHealth Platform (http://www.ehealth.fgov.be/, support@be-ehealth-standards.atlassian.net)</t>
+  </si>
+  <si>
+    <t>Message Structure (support@be-ehealth-standards.atlassian.net(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -66,22 +66,22 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T15:00:45+00:00</t>
+    <t>2025-05-14T15:07:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>eHealth Platform</t>
+    <t>eHealth Platform Belgium</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>eHealth Platform (http://www.ehealth.fgov.be/, support@be-ehealth-standards.atlassian.net)</t>
-  </si>
-  <si>
-    <t>Message Structure (support@be-ehealth-standards.atlassian.net(Work))</t>
+    <t>eHealth Platform Belgium (https://www.ehealth.fgov.be/standards/fhir/, support@be-ehealth-standards.atlassian.net)</t>
+  </si>
+  <si>
+    <t>Message Structure eHealth (support@be-ehealth-standards.atlassian.net(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -66,22 +66,22 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T15:07:35+00:00</t>
+    <t>2025-05-14T15:08:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>eHealth Platform Belgium</t>
+    <t>eHealth Platform</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>eHealth Platform Belgium (https://www.ehealth.fgov.be/standards/fhir/, support@be-ehealth-standards.atlassian.net)</t>
-  </si>
-  <si>
-    <t>Message Structure eHealth (support@be-ehealth-standards.atlassian.net(Work))</t>
+    <t>eHealth Platform (http://www.ehealth.fgov.be/, support@be-ehealth-standards.atlassian.net)</t>
+  </si>
+  <si>
+    <t>Message Structure (support@be-ehealth-standards.atlassian.net(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -66,22 +66,22 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T15:08:16+00:00</t>
+    <t>2025-05-22T14:06:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>eHealth Platform</t>
+    <t>eHealth Platform Belgium</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>eHealth Platform (http://www.ehealth.fgov.be/, support@be-ehealth-standards.atlassian.net)</t>
-  </si>
-  <si>
-    <t>Message Structure (support@be-ehealth-standards.atlassian.net(Work))</t>
+    <t>eHealth Platform Belgium (https://www.ehealth.fgov.be/standards/fhir/, support@be-ehealth-standards.atlassian.net)</t>
+  </si>
+  <si>
+    <t>Message Structure eHealth (support@be-ehealth-standards.atlassian.net(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-22T14:43:01+00:00</t>
+    <t>2025-05-22T14:52:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-22T14:52:21+00:00</t>
+    <t>2025-06-11T04:00:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-11T04:00:37+00:00</t>
+    <t>2025-06-26T13:57:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-26T13:57:34+00:00</t>
+    <t>2025-07-16T16:47:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-16T16:47:23+00:00</t>
+    <t>2025-07-16T16:49:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
